--- a/environment/seed/sources/Shared/Finance/FP&A/FY27 plan/FY27 planning assumptions - v4 branch draft.xlsx
+++ b/environment/seed/sources/Shared/Finance/FP&A/FY27 plan/FY27 planning assumptions - v4 branch draft.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R141c36a1519d4358"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue and Service" sheetId="2" r:id="R7660620a6314465f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin and Accuracy" sheetId="3" r:id="R83af408e7fb544ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex and Workforce" sheetId="4" r:id="Rc783ccc4f2374963"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branches and Backlog" sheetId="5" r:id="Rcbf3cbcf88594002"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working Capital" sheetId="6" r:id="R641fba8d7bf248a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="7" r:id="Rd8be2a2aff7a4403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="rId5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue and Service" sheetId="2" r:id="rId6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin and Accuracy" sheetId="3" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex and Workforce" sheetId="4" r:id="rId8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branches and Backlog" sheetId="5" r:id="rId9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working Capital" sheetId="6" r:id="rId10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="7" r:id="rId11"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -276,7 +276,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{DA8F23B2-2ACF-4855-B1E0-8A97385FDB93}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{5EBBD62F-F892-7FD7-B5B8-0E89F652C3AC}"/>
 </xltc:personList>
 </file>
 
@@ -10501,7 +10501,7 @@
         <x:v>PLN-00867</x:v>
       </x:c>
       <x:c r="B17" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C17" s="28" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -10526,7 +10526,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K17" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L17" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10538,7 +10538,7 @@
         <x:v>PLN-00868</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C18" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10563,7 +10563,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K18" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L18" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10575,7 +10575,7 @@
         <x:v>PLN-00869</x:v>
       </x:c>
       <x:c r="B19" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C19" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10600,7 +10600,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K19" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L19" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10612,7 +10612,7 @@
         <x:v>PLN-00870</x:v>
       </x:c>
       <x:c r="B20" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C20" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -10630,14 +10630,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H20" s="31" t="n">
-        <x:v>2.06</x:v>
+        <x:v>4.12</x:v>
       </x:c>
       <x:c r="I20" s="28" t="str"/>
       <x:c r="J20" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K20" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L20" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10649,7 +10649,7 @@
         <x:v>PLN-00871</x:v>
       </x:c>
       <x:c r="B21" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C21" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10674,7 +10674,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K21" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L21" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10686,7 +10686,7 @@
         <x:v>PLN-00872</x:v>
       </x:c>
       <x:c r="B22" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C22" s="28" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -10711,7 +10711,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K22" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L22" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10723,7 +10723,7 @@
         <x:v>PLN-00873</x:v>
       </x:c>
       <x:c r="B23" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C23" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10748,7 +10748,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K23" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L23" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10760,7 +10760,7 @@
         <x:v>PLN-00874</x:v>
       </x:c>
       <x:c r="B24" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C24" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10785,7 +10785,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K24" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L24" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10797,7 +10797,7 @@
         <x:v>PLN-00875</x:v>
       </x:c>
       <x:c r="B25" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C25" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10822,7 +10822,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K25" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L25" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10834,7 +10834,7 @@
         <x:v>PLN-00876</x:v>
       </x:c>
       <x:c r="B26" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C26" s="28" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -10859,7 +10859,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K26" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L26" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10871,7 +10871,7 @@
         <x:v>PLN-00877</x:v>
       </x:c>
       <x:c r="B27" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C27" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10896,7 +10896,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K27" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L27" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10908,7 +10908,7 @@
         <x:v>PLN-00878</x:v>
       </x:c>
       <x:c r="B28" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C28" s="28" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -10933,7 +10933,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K28" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L28" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10945,7 +10945,7 @@
         <x:v>PLN-00879</x:v>
       </x:c>
       <x:c r="B29" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C29" s="28" t="str">
         <x:v>Project burn curve</x:v>
@@ -10970,7 +10970,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K29" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L29" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -10982,7 +10982,7 @@
         <x:v>PLN-00880</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C30" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -11007,7 +11007,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K30" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L30" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -11019,7 +11019,7 @@
         <x:v>PLN-00881</x:v>
       </x:c>
       <x:c r="B31" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C31" s="28" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -11044,7 +11044,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K31" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L31" s="34" t="str">
         <x:v>2026-06-24</x:v>
@@ -11056,7 +11056,7 @@
         <x:v>PLN-00882</x:v>
       </x:c>
       <x:c r="B32" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C32" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -11081,7 +11081,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K32" s="28" t="str">
-        <x:v>Earlier management working export</x:v>
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
       </x:c>
       <x:c r="L32" s="34" t="str">
         <x:v>2026-06-24</x:v>
